--- a/data/final/players_info.xlsx
+++ b/data/final/players_info.xlsx
@@ -564,7 +564,7 @@
         <v>36170.0</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>23</v>
